--- a/data/processed/hra_mapping_unterbrechungsursache.xlsx
+++ b/data/processed/hra_mapping_unterbrechungsursache.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>715</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1285</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="14">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>117</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>921</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
